--- a/main/ig/FRDeviceLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -217,7 +217,7 @@
     <t>Device.type</t>
   </si>
   <si>
-    <t>Device.note.text</t>
+    <t>Device.note</t>
   </si>
 </sst>
 </file>

--- a/main/ig/FRDeviceLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-device|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-dispositif-medical</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-dispositif-medical|0.1.0</t>
   </si>
   <si>
     <t>FRLMDevice</t>

--- a/main/ig/FRDeviceLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="69">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:45:34+00:00</t>
+    <t>2026-08-31T15:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-device|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDevice|0.1.0</t>
   </si>
   <si>
     <t/>
@@ -115,13 +115,16 @@
     <t>related-to</t>
   </si>
   <si>
+    <t>Supply.participant.participantRole.playingDevice</t>
+  </si>
+  <si>
     <t>FRCDADispositifMedical.participant.participantRole.playingDevice</t>
   </si>
   <si>
     <t>FRLMDevice.identifier</t>
   </si>
   <si>
-    <t>FRCDADispositifMedical.participant.participantRole.id</t>
+    <t>Supply.participant.participantRole.id</t>
   </si>
   <si>
     <t>FRLMDevice.udi</t>
@@ -130,7 +133,7 @@
     <t>FRLMDevice.name</t>
   </si>
   <si>
-    <t>FRCDADispositifMedical.text</t>
+    <t>Supply.text</t>
   </si>
   <si>
     <t>FRLMDevice.name.value</t>
@@ -142,7 +145,7 @@
     <t>equivalent</t>
   </si>
   <si>
-    <t>FRCDADispositifMedical.participant.participantRole.playingDevice.code</t>
+    <t>Supply.participant.participantRole.playingDevice.code</t>
   </si>
   <si>
     <t>FRLMDevice.note</t>
@@ -517,83 +520,85 @@
       <c r="D3" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="E3" s="2"/>
+      <c r="E3" t="s" s="2">
+        <v>34</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -635,7 +640,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -647,192 +652,192 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E17" s="2"/>
     </row>

--- a/main/ig/FRDeviceLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
